--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.04</t>
+          <t>£10.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -589,29 +589,29 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -710,29 +710,29 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£14.68</t>
+          <t>£14.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -831,29 +831,29 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£14.98</t>
+          <t>£14.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -952,29 +952,29 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1073,29 +1073,29 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1194,29 +1194,29 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1315,29 +1315,29 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£24.12</t>
+          <t>£24.01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1436,29 +1436,29 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£26.14</t>
+          <t>£26.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1557,29 +1557,29 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£25.81</t>
+          <t>£25.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1678,29 +1678,29 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£35.31</t>
+          <t>£33.59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1799,29 +1799,29 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£31.55</t>
+          <t>£31.39</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1920,29 +1920,29 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2041,29 +2041,29 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.85</t>
+          <t>£38.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2162,29 +2162,29 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£38.48</t>
+          <t>£38.28</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2283,29 +2283,29 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,29 +2501,29 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -2622,29 +2622,29 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2743,29 +2743,29 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -2864,29 +2864,29 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2985,29 +2985,29 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -3106,29 +3106,29 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3227,29 +3227,29 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,29 +3348,29 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -3469,29 +3469,29 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4ade9e5+80021]
-	GetHandleVerifier [0x0x7ff7d4adea40+80112]
-	(No symbol) [0x0x7ff7d486060f]
-	(No symbol) [0x0x7ff7d48b8854]
-	(No symbol) [0x0x7ff7d48b8b1c]
-	(No symbol) [0x0x7ff7d490c927]
-	(No symbol) [0x0x7ff7d48e126f]
-	(No symbol) [0x0x7ff7d490968a]
-	(No symbol) [0x0x7ff7d48e1003]
-	(No symbol) [0x0x7ff7d48a95d1]
-	(No symbol) [0x0x7ff7d48aa3f3]
-	GetHandleVerifier [0x0x7ff7d4d9dd8d+2960445]
-	GetHandleVerifier [0x0x7ff7d4d9804a+2936570]
-	GetHandleVerifier [0x0x7ff7d4db8a87+3070263]
-	GetHandleVerifier [0x0x7ff7d4af84ce+185214]
-	GetHandleVerifier [0x0x7ff7d4afff1f+216527]
-	GetHandleVerifier [0x0x7ff7d4ae7c24+117460]
-	GetHandleVerifier [0x0x7ff7d4ae7ddf+117903]
-	GetHandleVerifier [0x0x7ff7d4acdcb8+11112]
-	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
-	RtlUserThreadStart [0x0x7ffc3674c53c+44]
+	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
+	GetHandleVerifier [0x0x7ff71b87ea40+80112]
+	(No symbol) [0x0x7ff71b60060f]
+	(No symbol) [0x0x7ff71b658854]
+	(No symbol) [0x0x7ff71b658b1c]
+	(No symbol) [0x0x7ff71b6ac927]
+	(No symbol) [0x0x7ff71b68126f]
+	(No symbol) [0x0x7ff71b6a968a]
+	(No symbol) [0x0x7ff71b681003]
+	(No symbol) [0x0x7ff71b6495d1]
+	(No symbol) [0x0x7ff71b64a3f3]
+	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
+	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
+	GetHandleVerifier [0x0x7ff71b8984ce+185214]
+	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
+	GetHandleVerifier [0x0x7ff71b887c24+117460]
+	GetHandleVerifier [0x0x7ff71b887ddf+117903]
+	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
+	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
+	RtlUserThreadStart [0x0x7fff31aec53c+44]
 </t>
         </is>
       </c>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,29 +589,29 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -710,29 +710,29 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -831,29 +831,29 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -952,29 +952,29 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1073,29 +1073,29 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1194,29 +1194,29 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1315,29 +1315,29 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1436,29 +1436,29 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1557,29 +1557,29 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1678,29 +1678,29 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1799,29 +1799,29 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1920,29 +1920,29 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2041,29 +2041,29 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2162,29 +2162,29 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2283,29 +2283,29 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,29 +2501,29 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -2622,29 +2622,29 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>£37.58</t>
+          <t>£30.00</t>
         </is>
       </c>
     </row>
@@ -2743,29 +2743,29 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>£45.67</t>
+          <t>£35.83</t>
         </is>
       </c>
     </row>
@@ -2864,29 +2864,29 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>£50.69</t>
+          <t>£40.83</t>
         </is>
       </c>
     </row>
@@ -2985,29 +2985,29 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>£55.30</t>
+          <t>£45.83</t>
         </is>
       </c>
     </row>
@@ -3106,29 +3106,29 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3227,29 +3227,29 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,29 +3348,29 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -3469,29 +3469,29 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b87e9e5+80021]
-	GetHandleVerifier [0x0x7ff71b87ea40+80112]
-	(No symbol) [0x0x7ff71b60060f]
-	(No symbol) [0x0x7ff71b658854]
-	(No symbol) [0x0x7ff71b658b1c]
-	(No symbol) [0x0x7ff71b6ac927]
-	(No symbol) [0x0x7ff71b68126f]
-	(No symbol) [0x0x7ff71b6a968a]
-	(No symbol) [0x0x7ff71b681003]
-	(No symbol) [0x0x7ff71b6495d1]
-	(No symbol) [0x0x7ff71b64a3f3]
-	GetHandleVerifier [0x0x7ff71bb3dd8d+2960445]
-	GetHandleVerifier [0x0x7ff71bb3804a+2936570]
-	GetHandleVerifier [0x0x7ff71bb58a87+3070263]
-	GetHandleVerifier [0x0x7ff71b8984ce+185214]
-	GetHandleVerifier [0x0x7ff71b89ff1f+216527]
-	GetHandleVerifier [0x0x7ff71b887c24+117460]
-	GetHandleVerifier [0x0x7ff71b887ddf+117903]
-	GetHandleVerifier [0x0x7ff71b86dcb8+11112]
-	BaseThreadInitThunk [0x0x7fff2ff4e8d7+23]
-	RtlUserThreadStart [0x0x7fff31aec53c+44]
+	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
+	GetHandleVerifier [0x0x7ff6737fea40+80112]
+	(No symbol) [0x0x7ff67358060f]
+	(No symbol) [0x0x7ff6735d8854]
+	(No symbol) [0x0x7ff6735d8b1c]
+	(No symbol) [0x0x7ff67362c927]
+	(No symbol) [0x0x7ff67360126f]
+	(No symbol) [0x0x7ff67362968a]
+	(No symbol) [0x0x7ff673601003]
+	(No symbol) [0x0x7ff6735c95d1]
+	(No symbol) [0x0x7ff6735ca3f3]
+	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
+	GetHandleVerifier [0x0x7ff673ab804a+2936570]
+	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
+	GetHandleVerifier [0x0x7ff6738184ce+185214]
+	GetHandleVerifier [0x0x7ff67381ff1f+216527]
+	GetHandleVerifier [0x0x7ff673807c24+117460]
+	GetHandleVerifier [0x0x7ff673807ddf+117903]
+	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
+	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
         </is>
       </c>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
